--- a/exports/SAIL_full_report.xlsx
+++ b/exports/SAIL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>4.08</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44572.38541666666</v>
+        <v>44572.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>105.7</v>
+        <v>104.5</v>
       </c>
       <c r="I2" t="n">
         <v>105.27</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.69</v>
+        <v>-4.78</v>
       </c>
       <c r="L2" t="n">
-        <v>4.74</v>
+        <v>5.01</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.12</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.38541666666</v>
+        <v>44593.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>99.05</v>
+        <v>103.7</v>
       </c>
       <c r="I3" t="n">
         <v>102.7033688948729</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
-        <v>5.22</v>
+        <v>0.77</v>
       </c>
       <c r="L3" t="n">
         <v>4.11</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>9.98</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>101.45</v>
+        <v>98.3</v>
       </c>
       <c r="I4" t="n">
         <v>98.49492193606358</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.17</v>
+        <v>-5.21</v>
       </c>
       <c r="L4" t="n">
-        <v>4.73</v>
+        <v>5.93</v>
       </c>
       <c r="M4" t="n">
         <v>2.18</v>
       </c>
       <c r="N4" t="n">
-        <v>2.71</v>
+        <v>5.42</v>
       </c>
       <c r="O4" t="n">
         <v>5.33</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44617.55208333334</v>
+        <v>44620.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>91.8</v>
+        <v>95.2</v>
       </c>
       <c r="I5" t="n">
         <v>94.80664589186003</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>6.61</v>
+        <v>3.15</v>
       </c>
       <c r="L5" t="n">
         <v>2.09</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.1</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44650.38541666666</v>
+        <v>44650.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>98.3</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>98.13021056051505</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>3.26</v>
+        <v>2.57</v>
       </c>
       <c r="L6" t="n">
         <v>5.25</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>6.14</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44652.55208333334</v>
+        <v>44655.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>102.1</v>
+        <v>106</v>
       </c>
       <c r="I7" t="n">
         <v>103.6490704275584</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.56</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>4.92</v>
+        <v>9.06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="O7" t="n">
         <v>-1.01</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>7.24</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>107</v>
+        <v>102.9</v>
       </c>
       <c r="I8" t="n">
         <v>104.0051359688887</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9399999999999999</v>
+        <v>-2.92</v>
       </c>
       <c r="L8" t="n">
-        <v>2.83</v>
+        <v>3.21</v>
       </c>
       <c r="M8" t="n">
         <v>0.91</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.49</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44749.38541666666</v>
+        <v>44749.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>70.5</v>
+        <v>73.5</v>
       </c>
       <c r="I9" t="n">
         <v>71.15106542835275</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>78.83333333333333</v>
+        <v>79</v>
       </c>
       <c r="K9" t="n">
-        <v>31.49</v>
+        <v>28.57</v>
       </c>
       <c r="L9" t="n">
         <v>4.32</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.16</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44795.38541666666</v>
+        <v>44795.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>79.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>78.95345611175911</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>45.83333333333334</v>
+        <v>46</v>
       </c>
       <c r="K10" t="n">
-        <v>8.44</v>
+        <v>6.26</v>
       </c>
       <c r="L10" t="n">
         <v>6.73</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>6.69</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44816.38541666666</v>
+        <v>44816.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>82.75</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>83.32739244507485</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.95</v>
+        <v>-6.79</v>
       </c>
       <c r="L11" t="n">
-        <v>6.53</v>
+        <v>6.91</v>
       </c>
       <c r="M11" t="n">
         <v>1.5</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>4.63</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>82.09999999999999</v>
+        <v>80.55</v>
       </c>
       <c r="I12" t="n">
         <v>80.64233981393015</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.56</v>
+        <v>-3.42</v>
       </c>
       <c r="L12" t="n">
-        <v>1.74</v>
+        <v>3.48</v>
       </c>
       <c r="M12" t="n">
         <v>1.86</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>5.91</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44838.38541666666</v>
+        <v>44838.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>78.34999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>78.83557266599065</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>2.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>2.3</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.19</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44881.55208333334</v>
+        <v>44882.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>82.55</v>
+        <v>82.05</v>
       </c>
       <c r="I14" t="n">
         <v>82.09083276595287</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>43</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="K14" t="n">
-        <v>3.32</v>
+        <v>2.69</v>
       </c>
       <c r="L14" t="n">
         <v>4.57</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>6.64</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44896.38541666666</v>
+        <v>44896.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>85.55</v>
+        <v>85.8</v>
       </c>
       <c r="I15" t="n">
         <v>85.55629764930117</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.27</v>
+        <v>-4.57</v>
       </c>
       <c r="L15" t="n">
-        <v>4.94</v>
+        <v>5.12</v>
       </c>
       <c r="M15" t="n">
         <v>1.86</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>4.49</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44908.38541666666</v>
+        <v>44908.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>84.25</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I16" t="n">
         <v>84.18113681043079</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.81</v>
+        <v>-1.98</v>
       </c>
       <c r="L16" t="n">
         <v>3.21</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>4.91</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44922.38541666666</v>
+        <v>44922.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>80.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="I17" t="n">
         <v>80.62127948019841</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>4.76</v>
+        <v>3.92</v>
       </c>
       <c r="L17" t="n">
         <v>1.9</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.41</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44953.55208333334</v>
+        <v>44956.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>88.15000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I18" t="n">
         <v>87.52454560112412</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>31</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K18" t="n">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
       <c r="L18" t="n">
         <v>1.05</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.34</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>86</v>
+        <v>87.3</v>
       </c>
       <c r="I19" t="n">
         <v>86.75050837344719</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K19" t="n">
-        <v>1.26</v>
+        <v>-0.23</v>
       </c>
       <c r="L19" t="n">
         <v>6.03</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>5.44</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45008.55208333334</v>
+        <v>45009.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>85.90000000000001</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="I20" t="n">
         <v>84.45243012795596</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.6</v>
+        <v>-4.75</v>
       </c>
       <c r="L20" t="n">
-        <v>3.72</v>
+        <v>5.27</v>
       </c>
       <c r="M20" t="n">
         <v>1.32</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>4.48</v>
       </c>
       <c r="O20" t="n">
         <v>1.98</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.17</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45044.55208333334</v>
+        <v>45048.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>82.7</v>
+        <v>84.95</v>
       </c>
       <c r="I21" t="n">
         <v>84.14990234129169</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K21" t="n">
-        <v>0.54</v>
+        <v>-2.16</v>
       </c>
       <c r="L21" t="n">
         <v>2.29</v>
@@ -1638,7 +1889,7 @@
         <v>0.91</v>
       </c>
       <c r="N21" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
         <v>-4.48</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.8</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45064.38541666666</v>
+        <v>45064.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>83.09999999999999</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I22" t="n">
         <v>82.58818422723452</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.18</v>
+        <v>-3.06</v>
       </c>
       <c r="L22" t="n">
         <v>3.24</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>4.3</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>82.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="I23" t="n">
         <v>84.29538807792612</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3</v>
+        <v>-2.85</v>
       </c>
       <c r="L23" t="n">
-        <v>1.09</v>
+        <v>3.04</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="N23" t="n">
-        <v>0.73</v>
+        <v>2.74</v>
       </c>
       <c r="O23" t="n">
         <v>-0.54</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.75</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45146.55208333334</v>
+        <v>45147.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>92.75</v>
+        <v>91.8</v>
       </c>
       <c r="I24" t="n">
         <v>91.97117319940827</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>71.16666666666667</v>
+        <v>72</v>
       </c>
       <c r="K24" t="n">
-        <v>9.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L24" t="n">
         <v>3.42</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>4.33</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45167.38541666666</v>
+        <v>45167.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>88.45</v>
+        <v>88.55</v>
       </c>
       <c r="I25" t="n">
         <v>88.46086034535328</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="L25" t="n">
         <v>2.34</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.35</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="I26" t="n">
         <v>96.719370368136</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>12.93</v>
+        <v>7.85</v>
       </c>
       <c r="L26" t="n">
         <v>0.5600000000000001</v>
@@ -1923,7 +2234,7 @@
         <v>0.15</v>
       </c>
       <c r="N26" t="n">
-        <v>2.55</v>
+        <v>6.25</v>
       </c>
       <c r="O26" t="n">
         <v>1.9</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.6</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45236.38541666666</v>
+        <v>45236.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>86</v>
+        <v>87.25</v>
       </c>
       <c r="I27" t="n">
         <v>86.89600653543758</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>55</v>
+        <v>55.16666666666666</v>
       </c>
       <c r="K27" t="n">
-        <v>9.949999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="L27" t="n">
         <v>6.86</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.85</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>109.8</v>
+        <v>103.6</v>
       </c>
       <c r="I28" t="n">
         <v>107.4201972479691</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>43.83333333333334</v>
+        <v>44</v>
       </c>
       <c r="K28" t="n">
-        <v>25.85</v>
+        <v>18.74</v>
       </c>
       <c r="L28" t="n">
         <v>3.27</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>12.78</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45286.55208333334</v>
+        <v>45287.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>114.6</v>
+        <v>115.55</v>
       </c>
       <c r="I29" t="n">
         <v>115.2492214770468</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-10.62</v>
+        <v>-11.53</v>
       </c>
       <c r="L29" t="n">
-        <v>10.91</v>
+        <v>14.09</v>
       </c>
       <c r="M29" t="n">
         <v>1.19</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>8.57</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45300.38541666666</v>
+        <v>45300.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>115.65</v>
+        <v>114.25</v>
       </c>
       <c r="I30" t="n">
         <v>114.4315588119438</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>0.09</v>
+        <v>-1.13</v>
       </c>
       <c r="L30" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="M30" t="n">
         <v>0.33</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>7.75</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45316.38541666666</v>
+        <v>45316.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>117.7</v>
+        <v>119.35</v>
       </c>
       <c r="I31" t="n">
         <v>118.1600553235416</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.02</v>
+        <v>-4.46</v>
       </c>
       <c r="L31" t="n">
         <v>4.99</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>133.5</v>
+        <v>126.25</v>
       </c>
       <c r="I32" t="n">
         <v>132.1478267906404</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>15</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>11.86</v>
+        <v>5.78</v>
       </c>
       <c r="L32" t="n">
         <v>2.26</v>
@@ -2265,7 +2648,7 @@
         <v>0.14</v>
       </c>
       <c r="N32" t="n">
-        <v>4.27</v>
+        <v>7.53</v>
       </c>
       <c r="O32" t="n">
         <v>3.87</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>17.63</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45352.38541666666</v>
+        <v>45355.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>128.6</v>
+        <v>140.65</v>
       </c>
       <c r="I33" t="n">
         <v>132.1460762508362</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.86</v>
+        <v>-11.41</v>
       </c>
       <c r="L33" t="n">
-        <v>7.72</v>
+        <v>11.88</v>
       </c>
       <c r="M33" t="n">
-        <v>1.23</v>
+        <v>7.15</v>
       </c>
       <c r="N33" t="n">
-        <v>5.84</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O33" t="n">
         <v>-7.53</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>12.54</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>129.3</v>
+        <v>123.5</v>
       </c>
       <c r="I34" t="n">
         <v>128.7726104131404</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K34" t="n">
-        <v>-8.07</v>
+        <v>-12.19</v>
       </c>
       <c r="L34" t="n">
-        <v>8.640000000000001</v>
+        <v>14.11</v>
       </c>
       <c r="M34" t="n">
         <v>0.67</v>
       </c>
       <c r="N34" t="n">
-        <v>3.58</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="O34" t="n">
         <v>9.800000000000001</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>14.37</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>134.35</v>
+        <v>139.8</v>
       </c>
       <c r="I35" t="n">
         <v>136.1044742525259</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>-8.789999999999999</v>
+        <v>-13.2</v>
       </c>
       <c r="L35" t="n">
-        <v>10.69</v>
+        <v>13.81</v>
       </c>
       <c r="M35" t="n">
         <v>2.78</v>
       </c>
       <c r="N35" t="n">
-        <v>3.87</v>
+        <v>4.73</v>
       </c>
       <c r="O35" t="n">
         <v>-8.619999999999999</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.27</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45421.38541666666</v>
+        <v>45421.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>156.65</v>
+        <v>153.9</v>
       </c>
       <c r="I36" t="n">
         <v>155.199945268364</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K36" t="n">
-        <v>12.05</v>
+        <v>10.09</v>
       </c>
       <c r="L36" t="n">
         <v>3</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>9.59</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45430.38541666666</v>
+        <v>45433.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>168.1</v>
+        <v>173.95</v>
       </c>
       <c r="I37" t="n">
         <v>168.4266403102977</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.23</v>
+        <v>-13.03</v>
       </c>
       <c r="L37" t="n">
-        <v>11.5</v>
+        <v>13.45</v>
       </c>
       <c r="M37" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="N37" t="n">
         <v>4.65</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>10.03</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45442.38541666666</v>
+        <v>45442.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>159.9</v>
+        <v>159.1</v>
       </c>
       <c r="I38" t="n">
         <v>159.7173059871077</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K38" t="n">
-        <v>-8.08</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>8.710000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="M38" t="n">
         <v>0.86</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.22</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45476.55208333334</v>
+        <v>45477.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>151.5</v>
+        <v>152.11</v>
       </c>
       <c r="I39" t="n">
         <v>151.9754132392112</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K39" t="n">
-        <v>4.78</v>
+        <v>4.39</v>
       </c>
       <c r="L39" t="n">
         <v>5.59</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.25</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>148.65</v>
+        <v>142.83</v>
       </c>
       <c r="I40" t="n">
         <v>146.8740271786517</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.27</v>
+        <v>-6.1</v>
       </c>
       <c r="L40" t="n">
-        <v>3.79</v>
+        <v>7.11</v>
       </c>
       <c r="M40" t="n">
-        <v>0.05</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>2.97</v>
+        <v>4.35</v>
       </c>
       <c r="O40" t="n">
         <v>-0.2</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.18</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45504.38541666666</v>
+        <v>45504.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>150.94</v>
+        <v>153.65</v>
       </c>
       <c r="I41" t="n">
         <v>151.4637786408388</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.68</v>
+        <v>-7.58</v>
       </c>
       <c r="L41" t="n">
-        <v>5.97</v>
+        <v>7.83</v>
       </c>
       <c r="M41" t="n">
         <v>1.73</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.66</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>145.98</v>
+        <v>137.19</v>
       </c>
       <c r="I42" t="n">
         <v>141.8754789116811</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.99</v>
+        <v>-10.71</v>
       </c>
       <c r="L42" t="n">
-        <v>5.56</v>
+        <v>12.14</v>
       </c>
       <c r="M42" t="n">
-        <v>1.12</v>
+        <v>3.41</v>
       </c>
       <c r="N42" t="n">
-        <v>2.77</v>
+        <v>6.32</v>
       </c>
       <c r="O42" t="n">
         <v>3.78</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.25</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45530.38541666666</v>
+        <v>45530.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>135.7</v>
+        <v>137.68</v>
       </c>
       <c r="I43" t="n">
         <v>136.4885374129865</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>1.09</v>
+        <v>-0.36</v>
       </c>
       <c r="L43" t="n">
         <v>4.13</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.05</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45541.38541666666</v>
+        <v>45541.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>130.43</v>
+        <v>129.45</v>
       </c>
       <c r="I44" t="n">
         <v>129.9024205309021</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.27</v>
+        <v>-5.98</v>
       </c>
       <c r="L44" t="n">
         <v>6.81</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>5.32</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45558.55208333334</v>
+        <v>45559.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>129.84</v>
+        <v>134.19</v>
       </c>
       <c r="I45" t="n">
         <v>133.4847553003497</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.3</v>
+        <v>-3.66</v>
       </c>
       <c r="L45" t="n">
-        <v>3.82</v>
+        <v>4.34</v>
       </c>
       <c r="M45" t="n">
         <v>1.82</v>
       </c>
       <c r="N45" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="O45" t="n">
         <v>-1.28</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>6.68</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>139.5</v>
+        <v>131.61</v>
       </c>
       <c r="I46" t="n">
         <v>133.6306210774591</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K46" t="n">
-        <v>3.96</v>
+        <v>-1.92</v>
       </c>
       <c r="L46" t="n">
-        <v>2.16</v>
+        <v>2.59</v>
       </c>
       <c r="M46" t="n">
         <v>1.67</v>
       </c>
       <c r="N46" t="n">
-        <v>2.75</v>
+        <v>5.4</v>
       </c>
       <c r="O46" t="n">
         <v>3.2</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11.86</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>118.53</v>
+        <v>122.65</v>
       </c>
       <c r="I47" t="n">
         <v>121.3532263911654</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K47" t="n">
-        <v>9.94</v>
+        <v>6.81</v>
       </c>
       <c r="L47" t="n">
         <v>6.77</v>
@@ -3120,7 +3683,7 @@
         <v>1.41</v>
       </c>
       <c r="N47" t="n">
-        <v>3.88</v>
+        <v>4.21</v>
       </c>
       <c r="O47" t="n">
         <v>-5.4</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45607.55208333334</v>
+        <v>45608.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>116.08</v>
+        <v>114.96</v>
       </c>
       <c r="I48" t="n">
         <v>115.2704554426344</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.36</v>
+        <v>-6.27</v>
       </c>
       <c r="L48" t="n">
-        <v>6.34</v>
+        <v>6.51</v>
       </c>
       <c r="M48" t="n">
         <v>2.22</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>9.6</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45628.55208333334</v>
+        <v>45629.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>118.9</v>
+        <v>122.34</v>
       </c>
       <c r="I49" t="n">
         <v>119.0552775920517</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.43</v>
+        <v>-6.42</v>
       </c>
       <c r="L49" t="n">
-        <v>3.88</v>
+        <v>6.72</v>
       </c>
       <c r="M49" t="n">
         <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>1.85</v>
+        <v>3.28</v>
       </c>
       <c r="O49" t="n">
         <v>-1.47</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.64</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45643.38541666666</v>
+        <v>45643.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>122.54</v>
+        <v>120.96</v>
       </c>
       <c r="I50" t="n">
         <v>122.1727943306829</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>0.16</v>
+        <v>-1.13</v>
       </c>
       <c r="L50" t="n">
         <v>2.57</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.17</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45673.55208333334</v>
+        <v>45674.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>107.45</v>
+        <v>108.82</v>
       </c>
       <c r="I51" t="n">
         <v>108.0008167938661</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>11.17</v>
+        <v>10.04</v>
       </c>
       <c r="L51" t="n">
         <v>1.39</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>7.05</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45684.38541666666</v>
+        <v>45684.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>104.45</v>
+        <v>103.6</v>
       </c>
       <c r="I52" t="n">
         <v>103.6971073195629</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.02</v>
+        <v>-4.8</v>
       </c>
       <c r="L52" t="n">
-        <v>4.59</v>
+        <v>5.48</v>
       </c>
       <c r="M52" t="n">
         <v>0.89</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.47</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45700.55208333334</v>
+        <v>45701.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>105.5</v>
+        <v>110.71</v>
       </c>
       <c r="I53" t="n">
         <v>108.7591829056382</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.83</v>
+        <v>-6.86</v>
       </c>
       <c r="L53" t="n">
         <v>7.43</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>11.11</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45715.55208333334</v>
+        <v>45716.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>105.8</v>
+        <v>102.38</v>
       </c>
       <c r="I54" t="n">
         <v>103.091221586223</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.44</v>
+        <v>-7.52</v>
       </c>
       <c r="L54" t="n">
-        <v>7.87</v>
+        <v>8.23</v>
       </c>
       <c r="M54" t="n">
         <v>1.42</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>10.09</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>112.41</v>
+        <v>113.02</v>
       </c>
       <c r="I55" t="n">
         <v>112.7069412195965</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>-9.800000000000001</v>
+        <v>-10.39</v>
       </c>
       <c r="L55" t="n">
-        <v>10.28</v>
+        <v>12.23</v>
       </c>
       <c r="M55" t="n">
-        <v>0.46</v>
+        <v>0.97</v>
       </c>
       <c r="N55" t="n">
         <v>4.27</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>112.65</v>
+        <v>103.26</v>
       </c>
       <c r="I56" t="n">
         <v>111.4869938462103</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.33</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>7.45</v>
+        <v>10.33</v>
       </c>
       <c r="M56" t="n">
-        <v>1.39</v>
+        <v>10.04</v>
       </c>
       <c r="N56" t="n">
-        <v>4.91</v>
+        <v>6.99</v>
       </c>
       <c r="O56" t="n">
         <v>-1.12</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>10.2</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>112.58</v>
+        <v>113.4</v>
       </c>
       <c r="I57" t="n">
         <v>113.0922446240385</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K57" t="n">
-        <v>-9.029999999999999</v>
+        <v>-9.82</v>
       </c>
       <c r="L57" t="n">
-        <v>9.52</v>
+        <v>10.13</v>
       </c>
       <c r="M57" t="n">
         <v>2.61</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>112.1</v>
+        <v>108.44</v>
       </c>
       <c r="I58" t="n">
         <v>110.596022889431</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.15</v>
+        <v>-4.37</v>
       </c>
       <c r="L58" t="n">
-        <v>3.24</v>
+        <v>4.37</v>
       </c>
       <c r="M58" t="n">
         <v>1.64</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>8.77</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>108.95</v>
+        <v>117.38</v>
       </c>
       <c r="I59" t="n">
         <v>115.6196425268048</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.47</v>
+        <v>-8.24</v>
       </c>
       <c r="L59" t="n">
-        <v>3.38</v>
+        <v>8.91</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N59" t="n">
-        <v>0.47</v>
+        <v>8.31</v>
       </c>
       <c r="O59" t="n">
         <v>-4.58</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>9.82</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>130</v>
+        <v>128.75</v>
       </c>
       <c r="I60" t="n">
         <v>129.3392442963334</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K60" t="n">
-        <v>10.75</v>
+        <v>9.69</v>
       </c>
       <c r="L60" t="n">
         <v>4.24</v>
       </c>
       <c r="M60" t="n">
-        <v>1.52</v>
+        <v>2.65</v>
       </c>
       <c r="N60" t="n">
         <v>2.15</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>4.14</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>126.53</v>
+        <v>131.75</v>
       </c>
       <c r="I61" t="n">
         <v>131.2637546944288</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K61" t="n">
-        <v>1.72</v>
+        <v>-2.33</v>
       </c>
       <c r="L61" t="n">
-        <v>0.93</v>
+        <v>3.18</v>
       </c>
       <c r="M61" t="n">
-        <v>0.06</v>
+        <v>1.2</v>
       </c>
       <c r="N61" t="n">
-        <v>1.84</v>
+        <v>3.23</v>
       </c>
       <c r="O61" t="n">
         <v>-0.5</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.78</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>135.9</v>
+        <v>130.75</v>
       </c>
       <c r="I62" t="n">
         <v>131.6061552911013</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K62" t="n">
-        <v>3.15</v>
+        <v>-0.76</v>
       </c>
       <c r="L62" t="n">
         <v>2.81</v>
@@ -3975,7 +4718,7 @@
         <v>0.77</v>
       </c>
       <c r="N62" t="n">
-        <v>1.75</v>
+        <v>4.05</v>
       </c>
       <c r="O62" t="n">
         <v>3.23</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.83</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45902.55208333334</v>
+        <v>45903.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>122.9</v>
+        <v>127.8</v>
       </c>
       <c r="I63" t="n">
         <v>123.7563688581667</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K63" t="n">
-        <v>6</v>
+        <v>2.26</v>
       </c>
       <c r="L63" t="n">
         <v>3.96</v>
@@ -4032,7 +4787,7 @@
         <v>1.89</v>
       </c>
       <c r="N63" t="n">
-        <v>4.41</v>
+        <v>5.41</v>
       </c>
       <c r="O63" t="n">
         <v>-4.05</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.31</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45926.38541666666</v>
+        <v>45926.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>132.01</v>
+        <v>130.69</v>
       </c>
       <c r="I64" t="n">
         <v>131.3918838735227</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>3.29</v>
+        <v>2.26</v>
       </c>
       <c r="L64" t="n">
         <v>3.32</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>6.11</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45958.55208333334</v>
+        <v>45959.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>132.33</v>
+        <v>140.95</v>
       </c>
       <c r="I65" t="n">
         <v>135.9772276705095</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>32</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.25</v>
+        <v>-7.85</v>
       </c>
       <c r="L65" t="n">
-        <v>5.52</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M65" t="n">
         <v>0.89</v>
       </c>
       <c r="N65" t="n">
-        <v>3.41</v>
+        <v>5.81</v>
       </c>
       <c r="O65" t="n">
         <v>-4.27</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.19</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45981.55208333334</v>
+        <v>45982.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>138.3</v>
+        <v>136.3</v>
       </c>
       <c r="I66" t="n">
         <v>136.5952610701918</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.88</v>
+        <v>-3.3</v>
       </c>
       <c r="L66" t="n">
         <v>5.5</v>
@@ -4203,7 +4994,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>2.01</v>
+        <v>3.4</v>
       </c>
       <c r="O66" t="n">
         <v>5.81</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.05</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46013.55208333334</v>
+        <v>46014.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>129.91</v>
+        <v>132.68</v>
       </c>
       <c r="I67" t="n">
         <v>131.85721799756</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K67" t="n">
-        <v>4.69</v>
+        <v>2.66</v>
       </c>
       <c r="L67" t="n">
         <v>2.46</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.53</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46054.55208333334</v>
+        <v>46055.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>147.5</v>
+        <v>144.51</v>
       </c>
       <c r="I68" t="n">
         <v>146.5335472080623</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K68" t="n">
-        <v>11.17</v>
+        <v>8.92</v>
       </c>
       <c r="L68" t="n">
         <v>2.09</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>11.38</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46062.55208333334</v>
+        <v>46063.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>158.55</v>
+        <v>161.2</v>
       </c>
       <c r="I69" t="n">
         <v>160.9525873882002</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K69" t="n">
-        <v>-9.720000000000001</v>
+        <v>-11.55</v>
       </c>
       <c r="L69" t="n">
         <v>12.03</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>9.66</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>165.61</v>
+        <v>154.12</v>
       </c>
       <c r="I70" t="n">
         <v>154.4404625753008</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K70" t="n">
-        <v>2.74</v>
+        <v>-4.39</v>
       </c>
       <c r="L70" t="n">
         <v>5.68</v>
@@ -4431,7 +5270,7 @@
         <v>3.64</v>
       </c>
       <c r="N70" t="n">
-        <v>2.43</v>
+        <v>6.77</v>
       </c>
       <c r="O70" t="n">
         <v>1.36</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>11.77</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46114.55208333334</v>
+        <v>46118.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>154.4</v>
+        <v>159.71</v>
       </c>
       <c r="I71" t="n">
         <v>159.3163475898408</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.18</v>
+        <v>-3.63</v>
       </c>
       <c r="L71" t="n">
         <v>4.74</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>12.43</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>180</v>
+        <v>177.89</v>
       </c>
       <c r="I72" t="n">
         <v>178.0266618727106</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K72" t="n">
-        <v>12.7</v>
+        <v>11.38</v>
       </c>
       <c r="L72" t="n">
         <v>5.25</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>6.3</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46154.55208333334</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>175.35</v>
+        <v>201.27</v>
       </c>
       <c r="I73" t="n">
         <v>186.6285399127048</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>1.43</v>
+        <v>-13.14</v>
       </c>
       <c r="L73" t="n">
-        <v>1.69</v>
+        <v>13.44</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>14.83</v>
       </c>
       <c r="O73" t="n">
         <v>-2.58</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>14.5</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46177.55208333334</v>
+        <v>46178.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>196.01</v>
+        <v>189.39</v>
       </c>
       <c r="I74" t="n">
         <v>193.5863696772049</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K74" t="n">
-        <v>-2.61</v>
+        <v>-5.9</v>
       </c>
       <c r="L74" t="n">
         <v>12.4</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>9.69</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>165.95</v>
+        <v>171.07</v>
       </c>
       <c r="I75" t="n">
         <v>168.4411351761071</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K75" t="n">
-        <v>12.38</v>
+        <v>9.67</v>
       </c>
       <c r="L75" t="n">
         <v>4.65</v>
@@ -4716,7 +5615,7 @@
         <v>1.85</v>
       </c>
       <c r="N75" t="n">
-        <v>2.7</v>
+        <v>3.23</v>
       </c>
       <c r="O75" t="n">
         <v>-2.87</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>6.69</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46247.38541666666</v>
+        <v>46247.55208333334</v>
       </c>
       <c r="H76" t="n">
-        <v>169.9</v>
+        <v>167.66</v>
       </c>
       <c r="I76" t="n">
         <v>168.0699764522296</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.68</v>
+        <v>-1.99</v>
       </c>
       <c r="L76" t="n">
         <v>3.05</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>6.79</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46255.55208333334</v>
+        <v>46258.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>174</v>
+        <v>180.66</v>
       </c>
       <c r="I77" t="n">
         <v>177.0152920754503</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K77" t="n">
-        <v>-3.78</v>
+        <v>-7.75</v>
       </c>
       <c r="L77" t="n">
-        <v>5.57</v>
+        <v>7.93</v>
       </c>
       <c r="M77" t="n">
         <v>0.72</v>
       </c>
       <c r="N77" t="n">
-        <v>2.64</v>
+        <v>2.89</v>
       </c>
       <c r="O77" t="n">
         <v>-2.97</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>7.54</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46275.38541666666</v>
+        <v>46275.55208333334</v>
       </c>
       <c r="H78" t="n">
-        <v>184.48</v>
+        <v>183.79</v>
       </c>
       <c r="I78" t="n">
         <v>183.824589076997</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K78" t="n">
-        <v>2.11</v>
+        <v>1.73</v>
       </c>
       <c r="L78" t="n">
         <v>3.29</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>6.56</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46288.38541666666</v>
+        <v>46288.55208333334</v>
       </c>
       <c r="H79" t="n">
-        <v>183.16</v>
+        <v>185.1</v>
       </c>
       <c r="I79" t="n">
         <v>183.7747971737277</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K79" t="n">
-        <v>0.34</v>
+        <v>-0.71</v>
       </c>
       <c r="L79" t="n">
-        <v>0.51</v>
+        <v>1.04</v>
       </c>
       <c r="M79" t="n">
         <v>0.63</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>6.28</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46296.38541666666</v>
+        <v>46296.55208333334</v>
       </c>
       <c r="H80" t="n">
-        <v>175.08</v>
+        <v>174.25</v>
       </c>
       <c r="I80" t="n">
         <v>175.0780000778095</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K80" t="n">
-        <v>-5.41</v>
+        <v>-5.86</v>
       </c>
       <c r="L80" t="n">
-        <v>5.65</v>
+        <v>7.8</v>
       </c>
       <c r="M80" t="n">
         <v>1.7</v>
@@ -5010,7 +5969,19 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5061,6 +6032,12 @@
       <c r="Q81" t="n">
         <v>33</v>
       </c>
+      <c r="R81" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7163,7 +8140,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.8</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="6">
@@ -7173,7 +8150,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="7">
@@ -7183,7 +8160,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78.8</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -7193,7 +8170,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7203,7 +8180,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="10">
@@ -7213,7 +8190,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39.4</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="11">
@@ -7223,7 +8200,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -7233,7 +8210,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -7243,7 +8220,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>75.90000000000001</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -7253,7 +8230,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.34</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="15">
@@ -7263,7 +8240,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="16">
@@ -7273,7 +8250,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.67</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="17">
@@ -7283,7 +8260,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.49</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="18">
@@ -7293,7 +8270,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.6</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="19">
@@ -7303,7 +8280,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.76</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="20">
@@ -7313,7 +8290,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.32</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="21">
@@ -7323,7 +8300,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.4</v>
+        <v>14.11</v>
       </c>
     </row>
     <row r="22">
@@ -7333,7 +8310,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -7343,7 +8320,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -7353,7 +8330,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="25">
@@ -7363,7 +8340,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.4</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="26">
@@ -7373,7 +8350,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.66</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="27">
@@ -7383,7 +8360,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.87</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="28">
@@ -7393,7 +8370,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
